--- a/templates/PhieuTheoDoi.xlsx
+++ b/templates/PhieuTheoDoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62127101-14B4-A44A-9ABE-C4D06ED0C5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874832D9-1416-BA41-9696-79F692A5003D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{0927E01F-30C0-F34E-AA0C-516DFF35C7E2}"/>
   </bookViews>
@@ -626,7 +626,7 @@
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -645,7 +645,7 @@
       <c r="A8" s="7"/>
       <c r="B8" s="8" t="str">
         <f ca="1">"TP.Cao Lãnh. Ngày "&amp;DAY(NOW())&amp;" tháng "&amp;MONTH(NOW())&amp;" năm "&amp;YEAR(NOW())</f>
-        <v>TP.Cao Lãnh. Ngày 28 tháng 5 năm 2025</v>
+        <v>TP.Cao Lãnh. Ngày 29 tháng 5 năm 2025</v>
       </c>
       <c r="C8" s="7"/>
     </row>

--- a/templates/PhieuTheoDoi.xlsx
+++ b/templates/PhieuTheoDoi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874832D9-1416-BA41-9696-79F692A5003D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFC5D79-B594-A94F-A736-4055E58E12F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{0927E01F-30C0-F34E-AA0C-516DFF35C7E2}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>PHÒNG XÉT NGHIỆM Y KHOA ANH QUÂN</t>
   </si>
   <si>
-    <t>60 Đống Đa, Phường 2, TP. Cao Lãnh, Đồng Tháp.</t>
-  </si>
-  <si>
     <t>SỔ THEO DÕI KẾT QUẢ XÉT NGHIỆM</t>
   </si>
   <si>
@@ -66,6 +63,9 @@
   </si>
   <si>
     <t>CN. NGUYỄN CÔNG MẪN</t>
+  </si>
+  <si>
+    <t>60 Đống Đa, Phường Cao Lãnh, Đồng Tháp.</t>
   </si>
 </sst>
 </file>
@@ -596,14 +596,14 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="20" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -611,7 +611,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -619,7 +619,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -627,13 +627,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="11" t="s">
         <v>6</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,20 +645,20 @@
       <c r="A8" s="7"/>
       <c r="B8" s="8" t="str">
         <f ca="1">"TP.Cao Lãnh. Ngày "&amp;DAY(NOW())&amp;" tháng "&amp;MONTH(NOW())&amp;" năm "&amp;YEAR(NOW())</f>
-        <v>TP.Cao Lãnh. Ngày 29 tháng 5 năm 2025</v>
+        <v>TP.Cao Lãnh. Ngày 17 tháng 9 năm 2025</v>
       </c>
       <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
